--- a/sinnoh_cube.xlsx
+++ b/sinnoh_cube.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lev\PycharmProjects\pokemon-legends\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB4042B-395A-4D9F-8F09-7A0E297E66FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175A6393-531B-4FF9-8085-F9303808C0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="1492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="1493">
   <si>
     <t>hp</t>
   </si>
@@ -3025,9 +3025,6 @@
     <t>482-x</t>
   </si>
   <si>
-    <t>Take Heart</t>
-  </si>
-  <si>
     <t>Sunshine Cherrim</t>
   </si>
   <si>
@@ -3862,9 +3859,6 @@
     <t>Apply the effects of all Protocol Moves in your party to the user, Attack Strength is increased to 6.</t>
   </si>
   <si>
-    <t>Copy the effect of a Move the user or target knows.</t>
-  </si>
-  <si>
     <t>Select a Move from the target and then attack the target with this Move.</t>
   </si>
   <si>
@@ -4525,13 +4519,22 @@
     <t>New Species Pokémon</t>
   </si>
   <si>
-    <t>For each Transform Move the user knows: Deal 2 extra damage.</t>
-  </si>
-  <si>
-    <t>Genesis Blast</t>
-  </si>
-  <si>
-    <t>Ancestor of all Pokémon</t>
+    <t>Mischievous Mimicry</t>
+  </si>
+  <si>
+    <t>Heart Swap</t>
+  </si>
+  <si>
+    <t>Increase the Battle Fatigue of the user by 2.</t>
+  </si>
+  <si>
+    <t>Inflict the [confused] status on the target. Deals 4 extra damage to [steel]-Type Pokémon.</t>
+  </si>
+  <si>
+    <t>Mirage of the Past</t>
+  </si>
+  <si>
+    <t>Copy the effect of a Move the target knows.</t>
   </si>
 </sst>
 </file>
@@ -5177,7 +5180,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5216,6 +5219,7 @@
     <xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="55" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5851,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN415"/>
+  <dimension ref="A1:AO415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
@@ -5890,9 +5894,10 @@
     <col min="38" max="38" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -5987,7 +5992,7 @@
         <v>943</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="AG1" s="2" t="s">
         <v>968</v>
@@ -6013,8 +6018,9 @@
       <c r="AN1" s="2" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AO1" s="32"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>387</v>
       </c>
@@ -6138,7 +6144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>388</v>
       </c>
@@ -6262,7 +6268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>389</v>
       </c>
@@ -6389,7 +6395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>978</v>
       </c>
@@ -6401,7 +6407,7 @@
         <v>Torterra</v>
       </c>
       <c r="D5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E5" t="s">
         <v>2</v>
@@ -6516,7 +6522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>390</v>
       </c>
@@ -6640,7 +6646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>391</v>
       </c>
@@ -6768,7 +6774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>392</v>
       </c>
@@ -6895,7 +6901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>979</v>
       </c>
@@ -6907,7 +6913,7 @@
         <v>Infernape</v>
       </c>
       <c r="D9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
@@ -7022,7 +7028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>393</v>
       </c>
@@ -7146,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>394</v>
       </c>
@@ -7270,7 +7276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>395</v>
       </c>
@@ -7396,7 +7402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>980</v>
       </c>
@@ -7408,7 +7414,7 @@
         <v>Empoleon</v>
       </c>
       <c r="D13" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -7522,7 +7528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>396</v>
       </c>
@@ -7650,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>397</v>
       </c>
@@ -7778,7 +7784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>398</v>
       </c>
@@ -7917,7 +7923,7 @@
         <v>Staraptor</v>
       </c>
       <c r="D17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -8907,7 +8913,7 @@
         <v>Luxray</v>
       </c>
       <c r="D25" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
@@ -9363,7 +9369,7 @@
         <v/>
       </c>
       <c r="AC28" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AD28" t="str">
         <f>VLOOKUP(AC28,moves!A:B,2,FALSE)</f>
@@ -9403,7 +9409,7 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B29" t="s">
         <v>163</v>
@@ -9413,7 +9419,7 @@
         <v>Roserade</v>
       </c>
       <c r="D29" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E29" t="s">
         <v>2</v>
@@ -9490,7 +9496,7 @@
         <v/>
       </c>
       <c r="AC29" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AD29" t="str">
         <f>VLOOKUP(AC29,moves!A:B,2,FALSE)</f>
@@ -10024,7 +10030,7 @@
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B34" t="s">
         <v>168</v>
@@ -10157,7 +10163,7 @@
         <v>Wormadam</v>
       </c>
       <c r="D35" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -10285,7 +10291,7 @@
         <v>970</v>
       </c>
       <c r="D36" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -10413,7 +10419,7 @@
         <v>971</v>
       </c>
       <c r="D37" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -10619,7 +10625,7 @@
         <v/>
       </c>
       <c r="AC38" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AD38" t="str">
         <f>VLOOKUP(AC38,moves!A:B,2,FALSE)</f>
@@ -11406,7 +11412,7 @@
         <v>Cherrim</v>
       </c>
       <c r="D45" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E45" t="s">
         <v>2</v>
@@ -11482,7 +11488,7 @@
         <v/>
       </c>
       <c r="AC45" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AD45" t="str">
         <f>VLOOKUP(AC45,moves!A:B,2,FALSE)</f>
@@ -11528,10 +11534,10 @@
         <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D46" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E46" t="s">
         <v>2</v>
@@ -11656,7 +11662,7 @@
         <v>438</v>
       </c>
       <c r="D47" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E47" t="s">
         <v>6</v>
@@ -11781,7 +11787,7 @@
         <v>439</v>
       </c>
       <c r="D48" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
@@ -11907,7 +11913,7 @@
         <v>440</v>
       </c>
       <c r="D49" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E49" t="s">
         <v>6</v>
@@ -12032,7 +12038,7 @@
         <v>441</v>
       </c>
       <c r="D50" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
@@ -13131,16 +13137,16 @@
     </row>
     <row r="59" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B59" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C59" t="s">
         <v>183</v>
       </c>
       <c r="D59" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E59" t="s">
         <v>42</v>
@@ -13170,7 +13176,7 @@
         <v>591</v>
       </c>
       <c r="O59" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P59">
         <f t="shared" ref="P59" si="58">(0.4*L59 + 0.5*MAX(H59,J59) + 0.1*MIN(H59,J59)) / 10</f>
@@ -13217,7 +13223,7 @@
         <v/>
       </c>
       <c r="AC59" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AD59" t="str">
         <f>VLOOKUP(AC59,moves!A:B,2,FALSE)</f>
@@ -14085,7 +14091,7 @@
         <v>6</v>
       </c>
       <c r="AC66" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="AD66" t="str">
         <f>VLOOKUP(AC66,moves!A:B,2,FALSE)</f>
@@ -15567,7 +15573,7 @@
         <v/>
       </c>
       <c r="AC78" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AD78" t="str">
         <f>VLOOKUP(AC78,moves!A:B,2,FALSE)</f>
@@ -15984,16 +15990,16 @@
     </row>
     <row r="82" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B82" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C82" t="s">
         <v>199</v>
       </c>
       <c r="D82" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -16023,7 +16029,7 @@
         <v>591</v>
       </c>
       <c r="O82" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P82">
         <f t="shared" ref="P82" si="73">(0.4*L82 + 0.5*MAX(H82,J82) + 0.1*MIN(H82,J82)) / 10</f>
@@ -16070,7 +16076,7 @@
         <v/>
       </c>
       <c r="AC82" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AD82" t="str">
         <f>VLOOKUP(AC82,moves!A:B,2,FALSE)</f>
@@ -16351,16 +16357,16 @@
     </row>
     <row r="85" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B85" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C85" t="s">
         <v>62</v>
       </c>
       <c r="D85" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -16390,7 +16396,7 @@
         <v>591</v>
       </c>
       <c r="O85" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P85">
         <f t="shared" ref="P85" si="79">(0.4*L85 + 0.5*MAX(H85,J85) + 0.1*MIN(H85,J85)) / 10</f>
@@ -16437,7 +16443,7 @@
         <v/>
       </c>
       <c r="AC85" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AD85" t="str">
         <f>VLOOKUP(AC85,moves!A:B,2,FALSE)</f>
@@ -16722,16 +16728,16 @@
     </row>
     <row r="88" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B88" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C88" t="s">
         <v>202</v>
       </c>
       <c r="D88" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E88" t="s">
         <v>22</v>
@@ -16761,7 +16767,7 @@
         <v>591</v>
       </c>
       <c r="O88" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P88">
         <f t="shared" ref="P88" si="85">(0.4*L88 + 0.5*MAX(H88,J88) + 0.1*MIN(H88,J88)) / 10</f>
@@ -16808,7 +16814,7 @@
         <v/>
       </c>
       <c r="AC88" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AD88" t="str">
         <f>VLOOKUP(AC88,moves!A:B,2,FALSE)</f>
@@ -17052,7 +17058,7 @@
         <v/>
       </c>
       <c r="AC90" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AD90" t="str">
         <f>VLOOKUP(AC90,moves!A:B,2,FALSE)</f>
@@ -17341,16 +17347,16 @@
     </row>
     <row r="93" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B93" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C93" t="s">
         <v>206</v>
       </c>
       <c r="D93" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="E93" t="s">
         <v>39</v>
@@ -17380,7 +17386,7 @@
         <v>591</v>
       </c>
       <c r="O93" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P93">
         <f t="shared" ref="P93" si="91">(0.4*L93 + 0.5*MAX(H93,J93) + 0.1*MIN(H93,J93)) / 10</f>
@@ -17427,7 +17433,7 @@
         <v/>
       </c>
       <c r="AC93" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AD93" t="str">
         <f>VLOOKUP(AC93,moves!A:B,2,FALSE)</f>
@@ -18828,16 +18834,16 @@
     </row>
     <row r="105" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B105" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C105" t="s">
         <v>214</v>
       </c>
       <c r="D105" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E105" t="s">
         <v>5</v>
@@ -18867,7 +18873,7 @@
         <v>591</v>
       </c>
       <c r="O105" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P105">
         <f t="shared" ref="P105" si="99">(0.4*L105 + 0.5*MAX(H105,J105) + 0.1*MIN(H105,J105)) / 10</f>
@@ -18914,7 +18920,7 @@
         <v/>
       </c>
       <c r="AC105" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="AD105" t="str">
         <f>VLOOKUP(AC105,moves!A:B,2,FALSE)</f>
@@ -20414,7 +20420,7 @@
         <v/>
       </c>
       <c r="AC117" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AD117" t="str">
         <f>VLOOKUP(AC117,moves!A:B,2,FALSE)</f>
@@ -20819,16 +20825,16 @@
     </row>
     <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B121" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C121" t="s">
         <v>220</v>
       </c>
       <c r="D121" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
@@ -20858,7 +20864,7 @@
         <v>591</v>
       </c>
       <c r="O121" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P121">
         <f t="shared" ref="P121" si="107">(0.4*L121 + 0.5*MAX(H121,J121) + 0.1*MIN(H121,J121)) / 10</f>
@@ -20905,7 +20911,7 @@
         <v/>
       </c>
       <c r="AC121" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="AD121" t="str">
         <f>VLOOKUP(AC121,moves!A:B,2,FALSE)</f>
@@ -21310,16 +21316,16 @@
     </row>
     <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B125" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C125" t="s">
         <v>221</v>
       </c>
       <c r="D125" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="E125" t="s">
         <v>4</v>
@@ -21349,7 +21355,7 @@
         <v>591</v>
       </c>
       <c r="O125" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P125">
         <f t="shared" ref="P125" si="114">(0.4*L125 + 0.5*MAX(H125,J125) + 0.1*MIN(H125,J125)) / 10</f>
@@ -21396,7 +21402,7 @@
         <v/>
       </c>
       <c r="AC125" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AD125" t="str">
         <f>VLOOKUP(AC125,moves!A:B,2,FALSE)</f>
@@ -21520,7 +21526,7 @@
         <v>4</v>
       </c>
       <c r="AC126" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AD126" t="str">
         <f>VLOOKUP(AC126,moves!A:B,2,FALSE)</f>
@@ -21822,7 +21828,7 @@
         <v>Togekiss</v>
       </c>
       <c r="D129" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -22191,16 +22197,16 @@
     </row>
     <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B132" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C132" t="s">
         <v>223</v>
       </c>
       <c r="D132" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E132" t="s">
         <v>7</v>
@@ -22230,7 +22236,7 @@
         <v>591</v>
       </c>
       <c r="O132" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P132">
         <f t="shared" ref="P132" si="129">(0.4*L132 + 0.5*MAX(H132,J132) + 0.1*MIN(H132,J132)) / 10</f>
@@ -22277,7 +22283,7 @@
         <v/>
       </c>
       <c r="AC132" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="AD132" t="str">
         <f>VLOOKUP(AC132,moves!A:B,2,FALSE)</f>
@@ -23000,7 +23006,7 @@
         <v/>
       </c>
       <c r="AC138" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AD138" t="str">
         <f>VLOOKUP(AC138,moves!A:B,2,FALSE)</f>
@@ -23120,7 +23126,7 @@
         <v/>
       </c>
       <c r="AC139" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AD139" t="str">
         <f>VLOOKUP(AC139,moves!A:B,2,FALSE)</f>
@@ -24042,7 +24048,7 @@
         <v>Mamoswine</v>
       </c>
       <c r="D147" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E147" t="s">
         <v>14</v>
@@ -25291,7 +25297,7 @@
         <v>Dusknoir</v>
       </c>
       <c r="D157" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E157" t="s">
         <v>42</v>
@@ -25733,7 +25739,7 @@
         <v/>
       </c>
       <c r="AC160" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="AD160" t="str">
         <f>VLOOKUP(AC160,moves!A:B,2,FALSE)</f>
@@ -25906,7 +25912,7 @@
         <v>946</v>
       </c>
       <c r="D162" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E162" t="s">
         <v>11</v>
@@ -26035,7 +26041,7 @@
         <v>947</v>
       </c>
       <c r="D163" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E163" t="s">
         <v>11</v>
@@ -26164,7 +26170,7 @@
         <v>948</v>
       </c>
       <c r="D164" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E164" t="s">
         <v>11</v>
@@ -26293,7 +26299,7 @@
         <v>949</v>
       </c>
       <c r="D165" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E165" t="s">
         <v>11</v>
@@ -26422,7 +26428,7 @@
         <v>950</v>
       </c>
       <c r="D166" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E166" t="s">
         <v>11</v>
@@ -26552,7 +26558,7 @@
         <v>Dialga</v>
       </c>
       <c r="D167" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="E167" t="s">
         <v>39</v>
@@ -26596,7 +26602,7 @@
         <v>0</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167">
         <f t="shared" si="148"/>
@@ -26604,11 +26610,11 @@
       </c>
       <c r="U167">
         <f t="shared" si="149"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V167">
         <f t="shared" si="150"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W167" t="str">
         <f t="shared" si="145"/>
@@ -26637,7 +26643,7 @@
       </c>
       <c r="AE167">
         <f>VLOOKUP(AC167,moves!A:D,4,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF167" t="str">
         <f>IF(VLOOKUP(AC167,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC167,moves!A:F,5,FALSE))</f>
@@ -26645,7 +26651,7 @@
       </c>
       <c r="AG167" t="str">
         <f>VLOOKUP(AC167,moves!A:F,6,FALSE)</f>
-        <v>Increase the Battle Fatigue of the user by 1.</v>
+        <v>Increase the Battle Fatigue of the user by 2.</v>
       </c>
       <c r="AH167">
         <v>0</v>
@@ -26675,10 +26681,10 @@
         <v>236</v>
       </c>
       <c r="C168" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D168" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E168" t="s">
         <v>39</v>
@@ -26690,7 +26696,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I168">
         <v>120</v>
@@ -26699,7 +26705,7 @@
         <v>150</v>
       </c>
       <c r="K168">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L168">
         <v>90</v>
@@ -26712,29 +26718,29 @@
       </c>
       <c r="P168">
         <f t="shared" ref="P168" si="170">(0.4*L168 + 0.5*MAX(H168,J168) + 0.1*MIN(H168,J168)) / 10</f>
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="Q168">
         <f t="shared" ref="Q168" si="171">(0.4*G168 + 0.3*I168 + 0.3*K168) / 10</f>
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T168">
         <f t="shared" ref="T168" si="172">ROUND(P168,0)+R168</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U168">
         <f t="shared" ref="U168" si="173">ROUND(Q168,0)+S168</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V168">
         <f t="shared" ref="V168" si="174">SUM(ROUND(T168,0),ROUND(U168,0))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W168" t="str">
         <f t="shared" ref="W168" si="175">E168</f>
@@ -26755,7 +26761,7 @@
         <v/>
       </c>
       <c r="AC168" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AD168" t="str">
         <f>VLOOKUP(AC168,moves!A:B,2,FALSE)</f>
@@ -26805,7 +26811,7 @@
         <v>Palkia</v>
       </c>
       <c r="D169" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E169" t="s">
         <v>6</v>
@@ -26846,22 +26852,22 @@
         <v>10.199999999999999</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T169">
         <f t="shared" si="148"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U169">
         <f t="shared" si="149"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V169">
         <f t="shared" si="150"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W169" t="str">
         <f t="shared" si="145"/>
@@ -26928,10 +26934,10 @@
         <v>237</v>
       </c>
       <c r="C170" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D170" t="s">
         <v>1188</v>
-      </c>
-      <c r="D170" t="s">
-        <v>1189</v>
       </c>
       <c r="E170" t="s">
         <v>6</v>
@@ -26943,7 +26949,7 @@
         <v>90</v>
       </c>
       <c r="H170">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I170">
         <v>100</v>
@@ -26955,7 +26961,7 @@
         <v>120</v>
       </c>
       <c r="L170">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="M170" t="s">
         <v>455</v>
@@ -26965,29 +26971,29 @@
       </c>
       <c r="P170">
         <f t="shared" ref="P170" si="176">(0.4*L170 + 0.5*MAX(H170,J170) + 0.1*MIN(H170,J170)) / 10</f>
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="Q170">
         <f t="shared" ref="Q170" si="177">(0.4*G170 + 0.3*I170 + 0.3*K170) / 10</f>
         <v>10.199999999999999</v>
       </c>
       <c r="R170">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T170">
         <f t="shared" ref="T170" si="178">ROUND(P170,0)+R170</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U170">
         <f t="shared" ref="U170" si="179">ROUND(Q170,0)+S170</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V170">
         <f t="shared" ref="V170" si="180">SUM(ROUND(T170,0),ROUND(U170,0))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W170" t="str">
         <f t="shared" ref="W170" si="181">E170</f>
@@ -27008,7 +27014,7 @@
         <v/>
       </c>
       <c r="AC170" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="AD170" t="str">
         <f>VLOOKUP(AC170,moves!A:B,2,FALSE)</f>
@@ -27016,7 +27022,7 @@
       </c>
       <c r="AE170">
         <f>VLOOKUP(AC170,moves!A:D,4,FALSE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF170" t="str">
         <f>IF(VLOOKUP(AC170,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC170,moves!A:F,5,FALSE))</f>
@@ -27024,7 +27030,7 @@
       </c>
       <c r="AG170" t="str">
         <f>VLOOKUP(AC170,moves!A:F,6,FALSE)</f>
-        <v>Increase the Battle Fatigue of the user by 1.</v>
+        <v>Increase the Battle Fatigue of the user by 2.</v>
       </c>
       <c r="AH170">
         <v>0</v>
@@ -27143,11 +27149,11 @@
       </c>
       <c r="AE171">
         <f>VLOOKUP(AC171,moves!A:D,4,FALSE)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF171" t="str">
         <f>IF(VLOOKUP(AC171,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC171,moves!A:F,5,FALSE))</f>
-        <v/>
+        <v>surge</v>
       </c>
       <c r="AG171" t="str">
         <f>VLOOKUP(AC171,moves!A:F,6,FALSE)</f>
@@ -27182,7 +27188,7 @@
         <v>Regigigas</v>
       </c>
       <c r="D172" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -27253,7 +27259,7 @@
         <v/>
       </c>
       <c r="AC172" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AD172" t="str">
         <f>VLOOKUP(AC172,moves!A:B,2,FALSE)</f>
@@ -27300,7 +27306,7 @@
         <v>Giratina</v>
       </c>
       <c r="D173" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="E173" t="s">
         <v>42</v>
@@ -27341,22 +27347,22 @@
         <v>13.2</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T173">
         <f t="shared" si="148"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U173">
         <f t="shared" si="149"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V173">
         <f t="shared" si="150"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W173" t="str">
         <f t="shared" si="145"/>
@@ -27426,7 +27432,7 @@
         <v>944</v>
       </c>
       <c r="D174" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E174" t="s">
         <v>42</v>
@@ -27467,22 +27473,22 @@
         <v>13.2</v>
       </c>
       <c r="R174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S174">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T174">
         <f t="shared" ref="T174" si="184">ROUND(P174,0)+R174</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U174">
         <f t="shared" ref="U174" si="185">ROUND(Q174,0)+S174</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V174">
         <f t="shared" ref="V174" si="186">SUM(ROUND(T174,0),ROUND(U174,0))</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W174" t="str">
         <f t="shared" ref="W174" si="187">E174</f>
@@ -27503,7 +27509,7 @@
         <v/>
       </c>
       <c r="AC174" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AD174" t="str">
         <f>VLOOKUP(AC174,moves!A:B,2,FALSE)</f>
@@ -27511,7 +27517,7 @@
       </c>
       <c r="AE174">
         <f>VLOOKUP(AC174,moves!A:D,4,FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF174" t="str">
         <f>IF(VLOOKUP(AC174,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC174,moves!A:F,5,FALSE))</f>
@@ -27866,7 +27872,7 @@
         <v/>
       </c>
       <c r="AC177" t="s">
-        <v>989</v>
+        <v>1488</v>
       </c>
       <c r="AD177" t="str">
         <f>VLOOKUP(AC177,moves!A:B,2,FALSE)</f>
@@ -28155,7 +28161,7 @@
         <v>951</v>
       </c>
       <c r="D180" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E180" t="s">
         <v>2</v>
@@ -28235,7 +28241,7 @@
         <v/>
       </c>
       <c r="AC180" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="AD180" t="str">
         <f>VLOOKUP(AC180,moves!A:B,2,FALSE)</f>
@@ -28730,7 +28736,7 @@
         <v/>
       </c>
       <c r="AC184" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="AD184" t="str">
         <f>VLOOKUP(AC184,moves!A:B,2,FALSE)</f>
@@ -28850,7 +28856,7 @@
         <v/>
       </c>
       <c r="AC185" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AD185" t="str">
         <f>VLOOKUP(AC185,moves!A:B,2,FALSE)</f>
@@ -28970,7 +28976,7 @@
         <v/>
       </c>
       <c r="AC186" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AD186" t="str">
         <f>VLOOKUP(AC186,moves!A:B,2,FALSE)</f>
@@ -29010,7 +29016,7 @@
         <v>894</v>
       </c>
       <c r="B187" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="194"/>
@@ -29038,7 +29044,7 @@
         <v>200</v>
       </c>
       <c r="M187" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="N187" t="s">
         <v>301</v>
@@ -29090,7 +29096,7 @@
         <v/>
       </c>
       <c r="AC187" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AD187" t="str">
         <f>VLOOKUP(AC187,moves!A:B,2,FALSE)</f>
@@ -29130,7 +29136,7 @@
         <v>895</v>
       </c>
       <c r="B188" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="194"/>
@@ -29158,7 +29164,7 @@
         <v>80</v>
       </c>
       <c r="M188" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="N188" t="s">
         <v>298</v>
@@ -29210,7 +29216,7 @@
         <v/>
       </c>
       <c r="AC188" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="AD188" t="str">
         <f>VLOOKUP(AC188,moves!A:B,2,FALSE)</f>
@@ -29582,7 +29588,7 @@
         <v>4</v>
       </c>
       <c r="AC191" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="AD191" t="str">
         <f>VLOOKUP(AC191,moves!A:B,2,FALSE)</f>
@@ -29866,7 +29872,7 @@
     </row>
     <row r="194" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B194" t="s">
         <v>12</v>
@@ -29876,7 +29882,7 @@
         <v>Raichu</v>
       </c>
       <c r="D194" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E194" t="s">
         <v>11</v>
@@ -30591,7 +30597,7 @@
         <v>5</v>
       </c>
       <c r="AC199" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AD199" t="str">
         <f>VLOOKUP(AC199,moves!A:B,2,FALSE)</f>
@@ -30839,7 +30845,7 @@
         <v>4</v>
       </c>
       <c r="AC201" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="AD201" t="str">
         <f>VLOOKUP(AC201,moves!A:B,2,FALSE)</f>
@@ -30963,7 +30969,7 @@
         <v>8</v>
       </c>
       <c r="AC202" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AD202" t="str">
         <f>VLOOKUP(AC202,moves!A:B,2,FALSE)</f>
@@ -31123,7 +31129,7 @@
     </row>
     <row r="204" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B204" t="s">
         <v>31</v>
@@ -31133,7 +31139,7 @@
         <v>Machamp</v>
       </c>
       <c r="D204" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E204" t="s">
         <v>22</v>
@@ -31701,7 +31707,7 @@
         <v/>
       </c>
       <c r="AC208" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="AD208" t="str">
         <f>VLOOKUP(AC208,moves!A:B,2,FALSE)</f>
@@ -31825,7 +31831,7 @@
         <v/>
       </c>
       <c r="AC209" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="AD209" t="str">
         <f>VLOOKUP(AC209,moves!A:B,2,FALSE)</f>
@@ -31949,7 +31955,7 @@
         <v/>
       </c>
       <c r="AC210" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AD210" t="str">
         <f>VLOOKUP(AC210,moves!A:B,2,FALSE)</f>
@@ -33949,11 +33955,11 @@
       </c>
       <c r="AF226" t="str">
         <f>IF(VLOOKUP(AC226,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC226,moves!A:F,5,FALSE))</f>
-        <v>dynamic</v>
+        <v/>
       </c>
       <c r="AG226" t="str">
         <f>VLOOKUP(AC226,moves!A:F,6,FALSE)</f>
-        <v>Copy the effect of a Move the user or target knows.</v>
+        <v>Inflict the [confused] status on the target. Deals 4 extra damage to [steel]-Type Pokémon.</v>
       </c>
       <c r="AH226">
         <v>0</v>
@@ -37635,7 +37641,7 @@
         <v/>
       </c>
       <c r="AC256" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AD256" t="str">
         <f>VLOOKUP(AC256,moves!A:B,2,FALSE)</f>
@@ -37675,7 +37681,7 @@
         <v>385</v>
       </c>
       <c r="B257" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="218"/>
@@ -37706,7 +37712,7 @@
         <v>100</v>
       </c>
       <c r="M257" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="N257" t="s">
         <v>304</v>
@@ -37759,7 +37765,7 @@
         <v/>
       </c>
       <c r="AC257" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="AD257" t="str">
         <f>VLOOKUP(AC257,moves!A:B,2,FALSE)</f>
@@ -38883,7 +38889,7 @@
         <v/>
       </c>
       <c r="AC266" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AD266" t="str">
         <f>VLOOKUP(AC266,moves!A:B,2,FALSE)</f>
@@ -40732,7 +40738,7 @@
         <v/>
       </c>
       <c r="AC281" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="AD281" t="str">
         <f>VLOOKUP(AC281,moves!A:B,2,FALSE)</f>
@@ -41107,7 +41113,7 @@
         <v/>
       </c>
       <c r="AC284" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AD284" t="str">
         <f>VLOOKUP(AC284,moves!A:B,2,FALSE)</f>
@@ -41470,7 +41476,7 @@
         <v/>
       </c>
       <c r="AC287" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AD287" t="str">
         <f>VLOOKUP(AC287,moves!A:B,2,FALSE)</f>
@@ -42138,7 +42144,7 @@
     </row>
     <row r="293" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B293" t="s">
         <v>136</v>
@@ -42148,7 +42154,7 @@
         <v>Walrein</v>
       </c>
       <c r="D293" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E293" t="s">
         <v>14</v>
@@ -42587,7 +42593,7 @@
         <v/>
       </c>
       <c r="AC296" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="AD296" t="str">
         <f>VLOOKUP(AC296,moves!A:B,2,FALSE)</f>
@@ -42627,7 +42633,7 @@
     </row>
     <row r="297" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B297" t="s">
         <v>459</v>
@@ -42637,7 +42643,7 @@
         <v>Porygon-Z</v>
       </c>
       <c r="D297" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -42710,7 +42716,7 @@
         <v/>
       </c>
       <c r="AC297" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="AD297" t="str">
         <f>VLOOKUP(AC297,moves!A:B,2,FALSE)</f>
@@ -42750,17 +42756,17 @@
     </row>
     <row r="298" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B298" t="s">
         <v>1190</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1191</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="228"/>
         <v>Prototype Zero</v>
       </c>
       <c r="D298" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E298" t="s">
         <v>548</v>
@@ -42787,7 +42793,7 @@
         <v>592</v>
       </c>
       <c r="O298" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P298">
         <f t="shared" ref="P298" si="246">(0.4*L298 + 0.5*MAX(H298,J298) + 0.1*MIN(H298,J298)) / 10</f>
@@ -42832,7 +42838,7 @@
         <v/>
       </c>
       <c r="AC298" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="AD298" t="str">
         <f>VLOOKUP(AC298,moves!A:B,2,FALSE)</f>
@@ -44240,7 +44246,7 @@
     </row>
     <row r="310" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B310" t="s">
         <v>709</v>
@@ -44250,7 +44256,7 @@
         <v>Chandelure</v>
       </c>
       <c r="D310" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E310" t="s">
         <v>42</v>
@@ -44750,7 +44756,7 @@
     </row>
     <row r="314" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B314" t="s">
         <v>730</v>
@@ -44760,7 +44766,7 @@
         <v>Decidueye</v>
       </c>
       <c r="D314" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E314" t="s">
         <v>2</v>
@@ -45088,7 +45094,7 @@
         <v>6</v>
       </c>
       <c r="AC316" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AD316" t="str">
         <f>VLOOKUP(AC316,moves!A:B,2,FALSE)</f>
@@ -45248,7 +45254,7 @@
     </row>
     <row r="318" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B318" t="s">
         <v>724</v>
@@ -45258,7 +45264,7 @@
         <v>Typhlosion</v>
       </c>
       <c r="D318" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E318" t="s">
         <v>4</v>
@@ -45742,7 +45748,7 @@
     </row>
     <row r="322" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B322" t="s">
         <v>739</v>
@@ -45752,7 +45758,7 @@
         <v>Samurott</v>
       </c>
       <c r="D322" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E322" t="s">
         <v>6</v>
@@ -46110,7 +46116,7 @@
     </row>
     <row r="325" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B325" t="s">
         <v>780</v>
@@ -46120,7 +46126,7 @@
         <v>Naganadel</v>
       </c>
       <c r="D325" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E325" t="s">
         <v>3</v>
@@ -46860,7 +46866,7 @@
         <v>690</v>
       </c>
       <c r="B331" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C331" t="str">
         <f t="shared" si="257"/>
@@ -46891,7 +46897,7 @@
         <v>30</v>
       </c>
       <c r="M331" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="N331" t="s">
         <v>303</v>
@@ -46947,7 +46953,7 @@
         <v>6</v>
       </c>
       <c r="AC331" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AD331" t="str">
         <f>VLOOKUP(AC331,moves!A:B,2,FALSE)</f>
@@ -46987,7 +46993,7 @@
         <v>691</v>
       </c>
       <c r="B332" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C332" t="str">
         <f t="shared" si="257"/>
@@ -47018,7 +47024,7 @@
         <v>44</v>
       </c>
       <c r="M332" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="N332" t="s">
         <v>303</v>
@@ -47862,7 +47868,7 @@
         <v>961</v>
       </c>
       <c r="D339" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E339" t="s">
         <v>39</v>
@@ -47991,7 +47997,7 @@
         <v>965</v>
       </c>
       <c r="D340" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
@@ -48114,7 +48120,7 @@
         <v>554</v>
       </c>
       <c r="B341" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C341" t="str">
         <f>B341</f>
@@ -48142,7 +48148,7 @@
         <v>50</v>
       </c>
       <c r="M341" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="N341" t="s">
         <v>301</v>
@@ -48198,7 +48204,7 @@
         <v>9</v>
       </c>
       <c r="AC341" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AD341" t="str">
         <f>VLOOKUP(AC341,moves!A:B,2,FALSE)</f>
@@ -48238,14 +48244,14 @@
         <v>555</v>
       </c>
       <c r="B342" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C342" t="str">
         <f>B342</f>
         <v>Darmanitan</v>
       </c>
       <c r="D342" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E342" t="s">
         <v>4</v>
@@ -48269,7 +48275,7 @@
         <v>95</v>
       </c>
       <c r="M342" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N342" t="s">
         <v>301</v>
@@ -48321,7 +48327,7 @@
         <v/>
       </c>
       <c r="AC342" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AD342" t="str">
         <f>VLOOKUP(AC342,moves!A:B,2,FALSE)</f>
@@ -48361,16 +48367,16 @@
     </row>
     <row r="343" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B343" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C343" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D343" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E343" t="s">
         <v>4</v>
@@ -48397,7 +48403,7 @@
         <v>55</v>
       </c>
       <c r="M343" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N343" t="s">
         <v>301</v>
@@ -48449,7 +48455,7 @@
         <v/>
       </c>
       <c r="AC343" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AD343" t="str">
         <f>VLOOKUP(AC343,moves!A:B,2,FALSE)</f>
@@ -48492,14 +48498,14 @@
         <v>877</v>
       </c>
       <c r="B344" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C344" t="str">
         <f>B344</f>
         <v>Morpeko</v>
       </c>
       <c r="D344" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E344" t="s">
         <v>11</v>
@@ -48526,7 +48532,7 @@
         <v>97</v>
       </c>
       <c r="M344" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="N344" t="s">
         <v>304</v>
@@ -48579,7 +48585,7 @@
         <v/>
       </c>
       <c r="AC344" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="AD344" t="str">
         <f>VLOOKUP(AC344,moves!A:B,2,FALSE)</f>
@@ -48619,16 +48625,16 @@
     </row>
     <row r="345" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C345" t="s">
         <v>1039</v>
       </c>
-      <c r="B345" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C345" t="s">
+      <c r="D345" t="s">
         <v>1040</v>
-      </c>
-      <c r="D345" t="s">
-        <v>1041</v>
       </c>
       <c r="E345" t="s">
         <v>11</v>
@@ -48655,7 +48661,7 @@
         <v>97</v>
       </c>
       <c r="M345" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="N345" t="s">
         <v>304</v>
@@ -48708,7 +48714,7 @@
         <v/>
       </c>
       <c r="AC345" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="AD345" t="str">
         <f>VLOOKUP(AC345,moves!A:B,2,FALSE)</f>
@@ -48751,7 +48757,7 @@
         <v>757</v>
       </c>
       <c r="B346" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C346" t="str">
         <f t="shared" ref="C346:C360" si="323">B346</f>
@@ -48782,7 +48788,7 @@
         <v>77</v>
       </c>
       <c r="M346" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="N346" t="s">
         <v>304</v>
@@ -48879,7 +48885,7 @@
         <v>758</v>
       </c>
       <c r="B347" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C347" t="str">
         <f t="shared" si="323"/>
@@ -48910,7 +48916,7 @@
         <v>117</v>
       </c>
       <c r="M347" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="N347" t="s">
         <v>304</v>
@@ -48963,7 +48969,7 @@
         <v/>
       </c>
       <c r="AC347" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="AD347" t="str">
         <f>VLOOKUP(AC347,moves!A:B,2,FALSE)</f>
@@ -49003,7 +49009,7 @@
         <v>633</v>
       </c>
       <c r="B348" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C348" t="str">
         <f t="shared" si="323"/>
@@ -49034,7 +49040,7 @@
         <v>38</v>
       </c>
       <c r="M348" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N348" t="s">
         <v>304</v>
@@ -49091,7 +49097,7 @@
         <v>4</v>
       </c>
       <c r="AC348" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AD348" t="str">
         <f>VLOOKUP(AC348,moves!A:B,2,FALSE)</f>
@@ -49131,7 +49137,7 @@
         <v>634</v>
       </c>
       <c r="B349" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C349" t="str">
         <f t="shared" si="323"/>
@@ -49259,7 +49265,7 @@
         <v>635</v>
       </c>
       <c r="B350" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C350" t="str">
         <f t="shared" si="323"/>
@@ -49290,7 +49296,7 @@
         <v>98</v>
       </c>
       <c r="M350" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="N350" t="s">
         <v>304</v>
@@ -49343,7 +49349,7 @@
         <v/>
       </c>
       <c r="AC350" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AD350" t="str">
         <f>VLOOKUP(AC350,moves!A:B,2,FALSE)</f>
@@ -49383,7 +49389,7 @@
         <v>636</v>
       </c>
       <c r="B351" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C351" t="str">
         <f t="shared" si="323"/>
@@ -49414,7 +49420,7 @@
         <v>60</v>
       </c>
       <c r="M351" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="N351" t="s">
         <v>298</v>
@@ -49511,7 +49517,7 @@
         <v>637</v>
       </c>
       <c r="B352" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C352" t="str">
         <f t="shared" si="323"/>
@@ -49595,7 +49601,7 @@
         <v/>
       </c>
       <c r="AC352" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AD352" t="str">
         <f>VLOOKUP(AC352,moves!A:B,2,FALSE)</f>
@@ -49635,7 +49641,7 @@
         <v>707</v>
       </c>
       <c r="B353" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C353" t="str">
         <f t="shared" si="323"/>
@@ -49666,7 +49672,7 @@
         <v>75</v>
       </c>
       <c r="M353" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="N353" t="s">
         <v>298</v>
@@ -49719,7 +49725,7 @@
         <v/>
       </c>
       <c r="AC353" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AD353" t="str">
         <f>VLOOKUP(AC353,moves!A:B,2,FALSE)</f>
@@ -49759,7 +49765,7 @@
         <v>703</v>
       </c>
       <c r="B354" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C354" t="str">
         <f t="shared" si="323"/>
@@ -49790,7 +49796,7 @@
         <v>50</v>
       </c>
       <c r="M354" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="O354" t="s">
         <v>549</v>
@@ -49840,7 +49846,7 @@
         <v/>
       </c>
       <c r="AC354" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AD354" t="str">
         <f>VLOOKUP(AC354,moves!A:B,2,FALSE)</f>
@@ -49880,7 +49886,7 @@
         <v>104</v>
       </c>
       <c r="B355" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C355" t="str">
         <f t="shared" si="323"/>
@@ -49908,7 +49914,7 @@
         <v>35</v>
       </c>
       <c r="M355" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="N355" t="s">
         <v>304</v>
@@ -49964,7 +49970,7 @@
         <v>6</v>
       </c>
       <c r="AC355" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AD355" t="str">
         <f>VLOOKUP(AC355,moves!A:B,2,FALSE)</f>
@@ -50004,7 +50010,7 @@
         <v>105</v>
       </c>
       <c r="B356" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C356" t="str">
         <f t="shared" si="323"/>
@@ -50032,7 +50038,7 @@
         <v>45</v>
       </c>
       <c r="M356" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="N356" t="s">
         <v>304</v>
@@ -50084,7 +50090,7 @@
         <v/>
       </c>
       <c r="AC356" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AD356" t="str">
         <f>VLOOKUP(AC356,moves!A:B,2,FALSE)</f>
@@ -50124,7 +50130,7 @@
         <v>374</v>
       </c>
       <c r="B357" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C357" t="str">
         <f t="shared" si="323"/>
@@ -50155,7 +50161,7 @@
         <v>30</v>
       </c>
       <c r="M357" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="O357" t="s">
         <v>549</v>
@@ -50201,7 +50207,7 @@
         <v>13</v>
       </c>
       <c r="AA357" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AB357">
         <f t="shared" si="294"/>
@@ -50248,7 +50254,7 @@
         <v>375</v>
       </c>
       <c r="B358" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C358" t="str">
         <f t="shared" si="323"/>
@@ -50279,7 +50285,7 @@
         <v>50</v>
       </c>
       <c r="M358" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="O358" t="s">
         <v>549</v>
@@ -50325,14 +50331,14 @@
         <v>13</v>
       </c>
       <c r="AA358" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AB358">
         <f t="shared" si="294"/>
         <v>9</v>
       </c>
       <c r="AC358" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AD358" t="str">
         <f>VLOOKUP(AC358,moves!A:B,2,FALSE)</f>
@@ -50372,7 +50378,7 @@
         <v>376</v>
       </c>
       <c r="B359" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C359" t="str">
         <f t="shared" si="323"/>
@@ -50403,7 +50409,7 @@
         <v>70</v>
       </c>
       <c r="M359" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="O359" t="s">
         <v>549</v>
@@ -50453,7 +50459,7 @@
         <v/>
       </c>
       <c r="AC359" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AD359" t="str">
         <f>VLOOKUP(AC359,moves!A:B,2,FALSE)</f>
@@ -50493,14 +50499,14 @@
         <v>774</v>
       </c>
       <c r="B360" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C360" t="str">
         <f t="shared" si="323"/>
         <v>Minior</v>
       </c>
       <c r="D360" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E360" t="s">
         <v>33</v>
@@ -50527,7 +50533,7 @@
         <v>90</v>
       </c>
       <c r="M360" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="O360" t="s">
         <v>549</v>
@@ -50577,7 +50583,7 @@
         <v/>
       </c>
       <c r="AC360" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="AD360" t="str">
         <f>VLOOKUP(AC360,moves!A:B,2,FALSE)</f>
@@ -50617,16 +50623,16 @@
     </row>
     <row r="361" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B361" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C361" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D361" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E361" t="s">
         <v>33</v>
@@ -50653,7 +50659,7 @@
         <v>90</v>
       </c>
       <c r="M361" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="O361" t="s">
         <v>549</v>
@@ -50703,7 +50709,7 @@
         <v/>
       </c>
       <c r="AC361" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AD361" t="str">
         <f>VLOOKUP(AC361,moves!A:B,2,FALSE)</f>
@@ -50746,7 +50752,7 @@
         <v>120</v>
       </c>
       <c r="B362" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C362" t="str">
         <f t="shared" ref="C362:C382" si="364">B362</f>
@@ -50774,7 +50780,7 @@
         <v>85</v>
       </c>
       <c r="M362" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="O362" t="s">
         <v>549</v>
@@ -50819,14 +50825,14 @@
         <v>8</v>
       </c>
       <c r="AA362" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AB362">
         <f t="shared" si="294"/>
         <v>8</v>
       </c>
       <c r="AC362" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="AD362" t="str">
         <f>VLOOKUP(AC362,moves!A:B,2,FALSE)</f>
@@ -50866,7 +50872,7 @@
         <v>121</v>
       </c>
       <c r="B363" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C363" t="str">
         <f t="shared" si="364"/>
@@ -50897,7 +50903,7 @@
         <v>115</v>
       </c>
       <c r="M363" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="O363" t="s">
         <v>549</v>
@@ -50987,7 +50993,7 @@
         <v>337</v>
       </c>
       <c r="B364" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C364" t="str">
         <f t="shared" si="364"/>
@@ -51018,7 +51024,7 @@
         <v>70</v>
       </c>
       <c r="M364" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="O364" t="s">
         <v>549</v>
@@ -51068,7 +51074,7 @@
         <v/>
       </c>
       <c r="AC364" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="AD364" t="str">
         <f>VLOOKUP(AC364,moves!A:B,2,FALSE)</f>
@@ -51108,7 +51114,7 @@
         <v>338</v>
       </c>
       <c r="B365" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C365" t="str">
         <f t="shared" si="364"/>
@@ -51139,7 +51145,7 @@
         <v>70</v>
       </c>
       <c r="M365" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="O365" t="s">
         <v>549</v>
@@ -51189,7 +51195,7 @@
         <v/>
       </c>
       <c r="AC365" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="AD365" t="str">
         <f>VLOOKUP(AC365,moves!A:B,2,FALSE)</f>
@@ -51617,7 +51623,7 @@
         <v>Arceus</v>
       </c>
       <c r="D369" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E369" t="s">
         <v>548</v>
@@ -51845,14 +51851,14 @@
         <v>249</v>
       </c>
       <c r="B371" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C371" t="str">
         <f t="shared" si="364"/>
         <v>Lugia</v>
       </c>
       <c r="D371" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E371" t="s">
         <v>26</v>
@@ -51879,7 +51885,7 @@
         <v>110</v>
       </c>
       <c r="M371" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="O371" t="s">
         <v>777</v>
@@ -51929,7 +51935,7 @@
         <v/>
       </c>
       <c r="AC371" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="AD371" t="str">
         <f>VLOOKUP(AC371,moves!A:B,2,FALSE)</f>
@@ -51969,7 +51975,7 @@
         <v>151</v>
       </c>
       <c r="B372" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C372" t="str">
         <f t="shared" si="364"/>
@@ -52000,7 +52006,7 @@
         <v>100</v>
       </c>
       <c r="M372" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="O372" t="s">
         <v>777</v>
@@ -52032,7 +52038,7 @@
         <v>20</v>
       </c>
       <c r="AC372" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="AD372" t="str">
         <f>VLOOKUP(AC372,moves!A:B,2,FALSE)</f>
@@ -52044,11 +52050,11 @@
       </c>
       <c r="AF372" t="str">
         <f>IF(VLOOKUP(AC372,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC372,moves!A:F,5,FALSE))</f>
-        <v>transform</v>
+        <v>dynamic</v>
       </c>
       <c r="AG372" t="str">
         <f>VLOOKUP(AC372,moves!A:F,6,FALSE)</f>
-        <v>For each Transform Move the user knows: Deal 2 extra damage.</v>
+        <v>Copy the effect of a Move the target knows.</v>
       </c>
       <c r="AH372">
         <v>0</v>
@@ -53029,7 +53035,7 @@
         <v/>
       </c>
       <c r="AC380" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="AD380" t="str">
         <f>VLOOKUP(AC380,moves!A:B,2,FALSE)</f>
@@ -56203,11 +56209,11 @@
       </c>
       <c r="AF404" t="str">
         <f>IF(VLOOKUP(AC404,moves!A:F,5,FALSE)=0, "", VLOOKUP(AC404,moves!A:F,5,FALSE))</f>
-        <v>dynamic</v>
+        <v/>
       </c>
       <c r="AG404" t="str">
         <f>VLOOKUP(AC404,moves!A:F,6,FALSE)</f>
-        <v>Copy the effect of a Move the user or target knows.</v>
+        <v>Inflict the [confused] status on the target. Deals 4 extra damage to [steel]-Type Pokémon.</v>
       </c>
       <c r="AH404">
         <v>0</v>
@@ -57809,7 +57815,7 @@
         <v>943</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>968</v>
@@ -57842,7 +57848,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">COUNT(IF(($A2=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -57876,7 +57882,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G3" cm="1">
         <f t="array" ref="G3">COUNT(IF(($A3=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -57910,7 +57916,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="G4" cm="1">
         <f t="array" ref="G4">COUNT(IF(($A4=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -57944,10 +57950,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F5" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G5" cm="1">
         <f t="array" ref="G5">COUNT(IF(($A5=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -57968,7 +57974,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>7</v>
@@ -57981,10 +57987,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F6" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G6" cm="1">
         <f t="array" ref="G6">COUNT(IF(($A6=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58018,7 +58024,7 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G7" cm="1">
         <f t="array" ref="G7">COUNT(IF(($A7=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58052,7 +58058,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G8" cm="1">
         <f t="array" ref="G8">COUNT(IF(($A8=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58086,10 +58092,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F9" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G9" cm="1">
         <f t="array" ref="G9">COUNT(IF(($A9=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58123,7 +58129,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G10" cm="1">
         <f t="array" ref="G10">COUNT(IF(($A10=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58144,7 +58150,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>7</v>
@@ -58157,7 +58163,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G11" cm="1">
         <f t="array" ref="G11">COUNT(IF(($A11=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58191,10 +58197,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F12" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G12" cm="1">
         <f t="array" ref="G12">COUNT(IF(($A12=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58228,7 +58234,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G13" cm="1">
         <f t="array" ref="G13">COUNT(IF(($A13=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58249,7 +58255,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>9</v>
@@ -58262,7 +58268,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G14" cm="1">
         <f t="array" ref="G14">COUNT(IF(($A14=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58296,10 +58302,10 @@
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F15" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="G15" cm="1">
         <f t="array" ref="G15">COUNT(IF(($A15=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58333,7 +58339,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G16" cm="1">
         <f t="array" ref="G16">COUNT(IF(($A16=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58367,7 +58373,7 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G17" cm="1">
         <f t="array" ref="G17">COUNT(IF(($A17=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58401,7 +58407,7 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G18" cm="1">
         <f t="array" ref="G18">COUNT(IF(($A18=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58422,7 +58428,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>9</v>
@@ -58435,10 +58441,10 @@
         <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F19" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G19" cm="1">
         <f t="array" ref="G19">COUNT(IF(($A19=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58459,7 +58465,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>9</v>
@@ -58472,10 +58478,10 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F20" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G20" cm="1">
         <f t="array" ref="G20">COUNT(IF(($A20=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58509,7 +58515,7 @@
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G21" cm="1">
         <f t="array" ref="G21">COUNT(IF(($A21=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58543,10 +58549,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F22" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G22" cm="1">
         <f t="array" ref="G22">COUNT(IF(($A22=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58567,7 +58573,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>9</v>
@@ -58580,7 +58586,7 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G23" cm="1">
         <f t="array" ref="G23">COUNT(IF(($A23=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58601,7 +58607,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>9</v>
@@ -58614,7 +58620,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="G24" cm="1">
         <f t="array" ref="G24">COUNT(IF(($A24=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58648,7 +58654,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G25" cm="1">
         <f t="array" ref="G25">COUNT(IF(($A25=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58669,7 +58675,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>67</v>
@@ -58682,7 +58688,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G26" cm="1">
         <f t="array" ref="G26">COUNT(IF(($A26=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58703,7 +58709,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>67</v>
@@ -58716,7 +58722,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G27" cm="1">
         <f t="array" ref="G27">COUNT(IF(($A27=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58750,7 +58756,7 @@
         <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G28" cm="1">
         <f t="array" ref="G28">COUNT(IF(($A28=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58758,11 +58764,11 @@
       </c>
       <c r="H28" cm="1">
         <f t="array" ref="H28">MIN(IF(($A28=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I28" cm="1">
         <f t="array" ref="I28">MAX(IF(($A28=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28">
         <f t="shared" si="1"/>
@@ -58784,7 +58790,7 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G29" cm="1">
         <f t="array" ref="G29">COUNT(IF(($A29=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58805,7 +58811,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>67</v>
@@ -58818,7 +58824,7 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G30" cm="1">
         <f t="array" ref="G30">COUNT(IF(($A30=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58852,7 +58858,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="G31" cm="1">
         <f t="array" ref="G31">COUNT(IF(($A31=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58873,17 +58879,17 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B32" s="18" t="s">
         <v>67</v>
       </c>
       <c r="C32">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>775</v>
@@ -58894,11 +58900,11 @@
       </c>
       <c r="H32" cm="1">
         <f t="array" ref="H32">MIN(IF(($A32=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I32" cm="1">
         <f t="array" ref="I32">MAX(IF(($A32=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J32">
         <f t="shared" si="1"/>
@@ -58920,7 +58926,7 @@
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G33" cm="1">
         <f t="array" ref="G33">COUNT(IF(($A33=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58947,17 +58953,17 @@
         <v>67</v>
       </c>
       <c r="C34">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D34">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F34" t="s">
-        <v>1258</v>
+        <v>1489</v>
       </c>
       <c r="G34" cm="1">
         <f t="array" ref="G34">COUNT(IF(($A34=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -58965,11 +58971,11 @@
       </c>
       <c r="H34" cm="1">
         <f t="array" ref="H34">MIN(IF(($A34=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I34" cm="1">
         <f t="array" ref="I34">MAX(IF(($A34=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34">
         <f t="shared" si="1"/>
@@ -58978,7 +58984,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>67</v>
@@ -58991,7 +58997,7 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G35" cm="1">
         <f t="array" ref="G35">COUNT(IF(($A35=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59012,7 +59018,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>67</v>
@@ -59025,10 +59031,10 @@
         <v>3</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F36" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="G36" cm="1">
         <f t="array" ref="G36">COUNT(IF(($A36=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59062,10 +59068,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F37" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G37" cm="1">
         <f t="array" ref="G37">COUNT(IF(($A37=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59099,7 +59105,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G38" cm="1">
         <f t="array" ref="G38">COUNT(IF(($A38=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59133,7 +59139,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G39" cm="1">
         <f t="array" ref="G39">COUNT(IF(($A39=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59167,7 +59173,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G40" cm="1">
         <f t="array" ref="G40">COUNT(IF(($A40=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59188,7 +59194,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>11</v>
@@ -59201,10 +59207,10 @@
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F41" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G41" cm="1">
         <f t="array" ref="G41">COUNT(IF(($A41=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59238,10 +59244,10 @@
         <v>3</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F42" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G42" cm="1">
         <f t="array" ref="G42">COUNT(IF(($A42=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59275,10 +59281,10 @@
         <v>3</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F43" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="G43" cm="1">
         <f t="array" ref="G43">COUNT(IF(($A43=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59312,7 +59318,7 @@
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="G44" cm="1">
         <f t="array" ref="G44">COUNT(IF(($A44=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59346,7 +59352,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G45" cm="1">
         <f t="array" ref="G45">COUNT(IF(($A45=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59380,7 +59386,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="G46" cm="1">
         <f t="array" ref="G46">COUNT(IF(($A46=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59401,7 +59407,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>11</v>
@@ -59414,10 +59420,10 @@
         <v>5</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F47" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G47" cm="1">
         <f t="array" ref="G47">COUNT(IF(($A47=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59451,7 +59457,7 @@
         <v>5</v>
       </c>
       <c r="F48" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="G48" cm="1">
         <f t="array" ref="G48">COUNT(IF(($A48=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59485,7 +59491,7 @@
         <v>5</v>
       </c>
       <c r="F49" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="G49" cm="1">
         <f t="array" ref="G49">COUNT(IF(($A49=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59516,10 +59522,10 @@
         <v/>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F50" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G50" cm="1">
         <f t="array" ref="G50">COUNT(IF(($A50=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59540,7 +59546,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>11</v>
@@ -59553,10 +59559,10 @@
         <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F51" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="G51" cm="1">
         <f t="array" ref="G51">COUNT(IF(($A51=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59577,7 +59583,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>11</v>
@@ -59590,10 +59596,10 @@
         <v>4</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F52" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G52" cm="1">
         <f t="array" ref="G52">COUNT(IF(($A52=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59626,10 +59632,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F53" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G53" cm="1">
         <f t="array" ref="G53">COUNT(IF(($A53=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59650,7 +59656,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>16</v>
@@ -59663,7 +59669,7 @@
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="G54" cm="1">
         <f t="array" ref="G54">COUNT(IF(($A54=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59697,10 +59703,10 @@
         <v>2</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F55" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G55" cm="1">
         <f t="array" ref="G55">COUNT(IF(($A55=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59734,7 +59740,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="G56" cm="1">
         <f t="array" ref="G56">COUNT(IF(($A56=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59755,7 +59761,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>16</v>
@@ -59768,7 +59774,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G57" cm="1">
         <f t="array" ref="G57">COUNT(IF(($A57=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59802,7 +59808,7 @@
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G58" cm="1">
         <f t="array" ref="G58">COUNT(IF(($A58=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59836,7 +59842,7 @@
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G59" cm="1">
         <f t="array" ref="G59">COUNT(IF(($A59=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59870,7 +59876,7 @@
         <v>5</v>
       </c>
       <c r="F60" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="G60" cm="1">
         <f t="array" ref="G60">COUNT(IF(($A60=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59891,7 +59897,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B61" s="21" t="s">
         <v>16</v>
@@ -59904,7 +59910,7 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="G61" cm="1">
         <f t="array" ref="G61">COUNT(IF(($A61=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59938,10 +59944,10 @@
         <v>2</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F62" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G62" cm="1">
         <f t="array" ref="G62">COUNT(IF(($A62=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59975,10 +59981,10 @@
         <v>2</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F63" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G63" cm="1">
         <f t="array" ref="G63">COUNT(IF(($A63=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -59999,7 +60005,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>22</v>
@@ -60012,10 +60018,10 @@
         <v>2</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F64" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G64" cm="1">
         <f t="array" ref="G64">COUNT(IF(($A64=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60049,7 +60055,7 @@
         <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="G65" cm="1">
         <f t="array" ref="G65">COUNT(IF(($A65=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60083,7 +60089,7 @@
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G66" cm="1">
         <f t="array" ref="G66">COUNT(IF(($A66=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60117,7 +60123,7 @@
         <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="G67" cm="1">
         <f t="array" ref="G67">COUNT(IF(($A67=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60151,7 +60157,7 @@
         <v>4</v>
       </c>
       <c r="F68" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G68" cm="1">
         <f t="array" ref="G68">COUNT(IF(($A68=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60185,7 +60191,7 @@
         <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G69" cm="1">
         <f t="array" ref="G69">COUNT(IF(($A69=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60219,7 +60225,7 @@
         <v>5</v>
       </c>
       <c r="F70" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="G70" cm="1">
         <f t="array" ref="G70">COUNT(IF(($A70=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60253,7 +60259,7 @@
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G71" cm="1">
         <f t="array" ref="G71">COUNT(IF(($A71=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60284,10 +60290,10 @@
         <v/>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F72" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G72" cm="1">
         <f t="array" ref="G72">COUNT(IF(($A72=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60321,10 +60327,10 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F73" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G73" cm="1">
         <f t="array" ref="G73">COUNT(IF(($A73=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60345,7 +60351,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>4</v>
@@ -60358,7 +60364,7 @@
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G74" cm="1">
         <f t="array" ref="G74">COUNT(IF(($A74=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60392,7 +60398,7 @@
         <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G75" cm="1">
         <f t="array" ref="G75">COUNT(IF(($A75=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60426,7 +60432,7 @@
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G76" cm="1">
         <f t="array" ref="G76">COUNT(IF(($A76=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60460,7 +60466,7 @@
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G77" cm="1">
         <f t="array" ref="G77">COUNT(IF(($A77=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60494,10 +60500,10 @@
         <v>3</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F78" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G78" cm="1">
         <f t="array" ref="G78">COUNT(IF(($A78=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60531,10 +60537,10 @@
         <v>3</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F79" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="G79" cm="1">
         <f t="array" ref="G79">COUNT(IF(($A79=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60568,7 +60574,7 @@
         <v>4</v>
       </c>
       <c r="F80" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="G80" cm="1">
         <f t="array" ref="G80">COUNT(IF(($A80=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60602,7 +60608,7 @@
         <v>4</v>
       </c>
       <c r="F81" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G81" cm="1">
         <f t="array" ref="G81">COUNT(IF(($A81=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60636,7 +60642,7 @@
         <v>4</v>
       </c>
       <c r="F82" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G82" cm="1">
         <f t="array" ref="G82">COUNT(IF(($A82=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60663,14 +60669,17 @@
         <v>4</v>
       </c>
       <c r="C83">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D83">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>1242</v>
       </c>
       <c r="F83" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="G83" cm="1">
         <f t="array" ref="G83">COUNT(IF(($A83=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60691,7 +60700,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>4</v>
@@ -60704,10 +60713,10 @@
         <v>4</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F84" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G84" cm="1">
         <f t="array" ref="G84">COUNT(IF(($A84=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60741,7 +60750,7 @@
         <v>5</v>
       </c>
       <c r="F85" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G85" cm="1">
         <f t="array" ref="G85">COUNT(IF(($A85=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60775,7 +60784,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G86" cm="1">
         <f t="array" ref="G86">COUNT(IF(($A86=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60796,7 +60805,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>4</v>
@@ -60809,10 +60818,10 @@
         <v>5</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F87" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G87" cm="1">
         <f t="array" ref="G87">COUNT(IF(($A87=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60846,7 +60855,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="G88" cm="1">
         <f t="array" ref="G88">COUNT(IF(($A88=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60880,7 +60889,7 @@
         <v>5</v>
       </c>
       <c r="F89" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="G89" cm="1">
         <f t="array" ref="G89">COUNT(IF(($A89=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60914,7 +60923,7 @@
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G90" cm="1">
         <f t="array" ref="G90">COUNT(IF(($A90=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60948,10 +60957,10 @@
         <v>9</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F91" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G91" cm="1">
         <f t="array" ref="G91">COUNT(IF(($A91=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -60972,7 +60981,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>4</v>
@@ -60985,10 +60994,10 @@
         <v>6</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F92" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G92" cm="1">
         <f t="array" ref="G92">COUNT(IF(($A92=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61019,10 +61028,10 @@
         <v/>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F93" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="G93" cm="1">
         <f t="array" ref="G93">COUNT(IF(($A93=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61056,7 +61065,7 @@
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G94" cm="1">
         <f t="array" ref="G94">COUNT(IF(($A94=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61090,7 +61099,7 @@
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G95" cm="1">
         <f t="array" ref="G95">COUNT(IF(($A95=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61124,10 +61133,10 @@
         <v>3</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F96" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G96" cm="1">
         <f t="array" ref="G96">COUNT(IF(($A96=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61148,7 +61157,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B97" s="13" t="s">
         <v>5</v>
@@ -61161,7 +61170,7 @@
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G97" cm="1">
         <f t="array" ref="G97">COUNT(IF(($A97=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61195,7 +61204,7 @@
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G98" cm="1">
         <f t="array" ref="G98">COUNT(IF(($A98=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61229,7 +61238,7 @@
         <v>4</v>
       </c>
       <c r="F99" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G99" cm="1">
         <f t="array" ref="G99">COUNT(IF(($A99=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61250,7 +61259,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B100" s="13" t="s">
         <v>5</v>
@@ -61263,7 +61272,7 @@
         <v>5</v>
       </c>
       <c r="F100" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G100" cm="1">
         <f t="array" ref="G100">COUNT(IF(($A100=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61297,7 +61306,7 @@
         <v>5</v>
       </c>
       <c r="F101" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G101" cm="1">
         <f t="array" ref="G101">COUNT(IF(($A101=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61331,10 +61340,10 @@
         <v>5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F102" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G102" cm="1">
         <f t="array" ref="G102">COUNT(IF(($A102=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61355,7 +61364,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B103" s="13" t="s">
         <v>5</v>
@@ -61368,10 +61377,10 @@
         <v>2</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F103" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G103" cm="1">
         <f t="array" ref="G103">COUNT(IF(($A103=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61405,10 +61414,10 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F104" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G104" cm="1">
         <f t="array" ref="G104">COUNT(IF(($A104=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61442,10 +61451,10 @@
         <v>2</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F105" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G105" cm="1">
         <f t="array" ref="G105">COUNT(IF(($A105=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61479,10 +61488,10 @@
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F106" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G106" cm="1">
         <f t="array" ref="G106">COUNT(IF(($A106=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61516,10 +61525,10 @@
         <v>2</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F107" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G107" cm="1">
         <f t="array" ref="G107">COUNT(IF(($A107=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61553,7 +61562,7 @@
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G108" cm="1">
         <f t="array" ref="G108">COUNT(IF(($A108=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61574,7 +61583,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B109" s="17" t="s">
         <v>42</v>
@@ -61587,10 +61596,10 @@
         <v>4</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F109" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G109" cm="1">
         <f t="array" ref="G109">COUNT(IF(($A109=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61624,10 +61633,10 @@
         <v>4</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F110" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G110" cm="1">
         <f t="array" ref="G110">COUNT(IF(($A110=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61661,7 +61670,7 @@
         <v>4</v>
       </c>
       <c r="F111" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G111" cm="1">
         <f t="array" ref="G111">COUNT(IF(($A111=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61695,7 +61704,7 @@
         <v>5</v>
       </c>
       <c r="F112" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G112" cm="1">
         <f t="array" ref="G112">COUNT(IF(($A112=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61703,11 +61712,11 @@
       </c>
       <c r="H112" cm="1">
         <f t="array" ref="H112">MIN(IF(($A112=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I112" cm="1">
         <f t="array" ref="I112">MAX(IF(($A112=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J112">
         <f t="shared" si="5"/>
@@ -61729,10 +61738,10 @@
         <v>6</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G113" cm="1">
         <f t="array" ref="G113">COUNT(IF(($A113=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61766,10 +61775,10 @@
         <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F114" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G114" cm="1">
         <f t="array" ref="G114">COUNT(IF(($A114=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61803,10 +61812,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F115" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G115" cm="1">
         <f t="array" ref="G115">COUNT(IF(($A115=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61827,7 +61836,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>2</v>
@@ -61840,10 +61849,10 @@
         <v>2</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F116" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G116" cm="1">
         <f t="array" ref="G116">COUNT(IF(($A116=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61877,7 +61886,7 @@
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G117" cm="1">
         <f t="array" ref="G117">COUNT(IF(($A117=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61911,7 +61920,7 @@
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G118" cm="1">
         <f t="array" ref="G118">COUNT(IF(($A118=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61945,7 +61954,7 @@
         <v>4</v>
       </c>
       <c r="F119" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G119" cm="1">
         <f t="array" ref="G119">COUNT(IF(($A119=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -61979,7 +61988,7 @@
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="G120" cm="1">
         <f t="array" ref="G120">COUNT(IF(($A120=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62013,7 +62022,7 @@
         <v>4</v>
       </c>
       <c r="F121" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G121" cm="1">
         <f t="array" ref="G121">COUNT(IF(($A121=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62034,7 +62043,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>2</v>
@@ -62047,10 +62056,10 @@
         <v>3</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F122" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G122" cm="1">
         <f t="array" ref="G122">COUNT(IF(($A122=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62084,7 +62093,7 @@
         <v>5</v>
       </c>
       <c r="F123" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G123" cm="1">
         <f t="array" ref="G123">COUNT(IF(($A123=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62118,7 +62127,7 @@
         <v>5</v>
       </c>
       <c r="F124" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G124" cm="1">
         <f t="array" ref="G124">COUNT(IF(($A124=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62152,10 +62161,10 @@
         <v>4</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F125" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G125" cm="1">
         <f t="array" ref="G125">COUNT(IF(($A125=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62210,7 +62219,7 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>2</v>
@@ -62223,10 +62232,10 @@
         <v>4</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F127" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G127" cm="1">
         <f t="array" ref="G127">COUNT(IF(($A127=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62247,7 +62256,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>2</v>
@@ -62260,7 +62269,7 @@
         <v>5</v>
       </c>
       <c r="F128" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G128" cm="1">
         <f t="array" ref="G128">COUNT(IF(($A128=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62294,10 +62303,10 @@
         <v>6</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F129" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G129" cm="1">
         <f t="array" ref="G129">COUNT(IF(($A129=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62318,7 +62327,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>2</v>
@@ -62331,7 +62340,7 @@
         <v>5</v>
       </c>
       <c r="F130" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G130" cm="1">
         <f t="array" ref="G130">COUNT(IF(($A130=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62352,7 +62361,7 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>2</v>
@@ -62365,7 +62374,7 @@
         <v>4</v>
       </c>
       <c r="F131" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="G131" cm="1">
         <f t="array" ref="G131">COUNT(IF(($A131=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62399,7 +62408,7 @@
         <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G132" cm="1">
         <f t="array" ref="G132">COUNT(IF(($A132=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62420,7 +62429,7 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>13</v>
@@ -62433,7 +62442,7 @@
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G133" cm="1">
         <f t="array" ref="G133">COUNT(IF(($A133=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62467,7 +62476,7 @@
         <v>3</v>
       </c>
       <c r="F134" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G134" cm="1">
         <f t="array" ref="G134">COUNT(IF(($A134=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62501,7 +62510,7 @@
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G135" cm="1">
         <f t="array" ref="G135">COUNT(IF(($A135=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62535,7 +62544,7 @@
         <v>5</v>
       </c>
       <c r="F136" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G136" cm="1">
         <f t="array" ref="G136">COUNT(IF(($A136=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62569,7 +62578,7 @@
         <v>5</v>
       </c>
       <c r="F137" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G137" cm="1">
         <f t="array" ref="G137">COUNT(IF(($A137=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62590,7 +62599,7 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B138" s="12" t="s">
         <v>13</v>
@@ -62603,7 +62612,7 @@
         <v>5</v>
       </c>
       <c r="F138" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="G138" cm="1">
         <f t="array" ref="G138">COUNT(IF(($A138=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62624,7 +62633,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>13</v>
@@ -62637,7 +62646,7 @@
         <v>6</v>
       </c>
       <c r="F139" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="G139" cm="1">
         <f t="array" ref="G139">COUNT(IF(($A139=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62671,7 +62680,7 @@
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G140" cm="1">
         <f t="array" ref="G140">COUNT(IF(($A140=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62705,7 +62714,7 @@
         <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G141" cm="1">
         <f t="array" ref="G141">COUNT(IF(($A141=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62739,7 +62748,7 @@
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G142" cm="1">
         <f t="array" ref="G142">COUNT(IF(($A142=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62760,7 +62769,7 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>14</v>
@@ -62773,10 +62782,10 @@
         <v>3</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F143" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G143" cm="1">
         <f t="array" ref="G143">COUNT(IF(($A143=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62810,7 +62819,7 @@
         <v>3</v>
       </c>
       <c r="F144" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G144" cm="1">
         <f t="array" ref="G144">COUNT(IF(($A144=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62844,7 +62853,7 @@
         <v>4</v>
       </c>
       <c r="F145" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G145" cm="1">
         <f t="array" ref="G145">COUNT(IF(($A145=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62878,7 +62887,7 @@
         <v>4</v>
       </c>
       <c r="F146" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="G146" cm="1">
         <f t="array" ref="G146">COUNT(IF(($A146=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62912,7 +62921,7 @@
         <v>4</v>
       </c>
       <c r="F147" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="G147" cm="1">
         <f t="array" ref="G147">COUNT(IF(($A147=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62933,7 +62942,7 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>14</v>
@@ -62946,7 +62955,7 @@
         <v>5</v>
       </c>
       <c r="F148" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G148" cm="1">
         <f t="array" ref="G148">COUNT(IF(($A148=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -62967,7 +62976,7 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B149" s="10" t="s">
         <v>14</v>
@@ -62980,10 +62989,10 @@
         <v>5</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F149" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G149" cm="1">
         <f t="array" ref="G149">COUNT(IF(($A149=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63017,7 +63026,7 @@
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G150" cm="1">
         <f t="array" ref="G150">COUNT(IF(($A150=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63051,7 +63060,7 @@
         <v>6</v>
       </c>
       <c r="F151" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="G151" cm="1">
         <f t="array" ref="G151">COUNT(IF(($A151=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63072,7 +63081,7 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>14</v>
@@ -63085,10 +63094,10 @@
         <v>3</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F152" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="G152" cm="1">
         <f t="array" ref="G152">COUNT(IF(($A152=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63122,10 +63131,10 @@
         <v>1</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F153" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G153" cm="1">
         <f t="array" ref="G153">COUNT(IF(($A153=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63159,10 +63168,10 @@
         <v>1</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F154" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="G154" cm="1">
         <f t="array" ref="G154">COUNT(IF(($A154=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63196,7 +63205,7 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G155" cm="1">
         <f t="array" ref="G155">COUNT(IF(($A155=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63230,10 +63239,10 @@
         <v>1</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F156" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G156" cm="1">
         <f t="array" ref="G156">COUNT(IF(($A156=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63267,10 +63276,10 @@
         <v>2</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F157" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G157" cm="1">
         <f t="array" ref="G157">COUNT(IF(($A157=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63304,7 +63313,7 @@
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G158" cm="1">
         <f t="array" ref="G158">COUNT(IF(($A158=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63338,7 +63347,7 @@
         <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G159" cm="1">
         <f t="array" ref="G159">COUNT(IF(($A159=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63372,7 +63381,7 @@
         <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G160" cm="1">
         <f t="array" ref="G160">COUNT(IF(($A160=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63406,10 +63415,10 @@
         <v>2</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F161" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G161" cm="1">
         <f t="array" ref="G161">COUNT(IF(($A161=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63443,7 +63452,7 @@
         <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G162" cm="1">
         <f t="array" ref="G162">COUNT(IF(($A162=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63477,10 +63486,10 @@
         <v>3</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F163" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G163" cm="1">
         <f t="array" ref="G163">COUNT(IF(($A163=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63514,7 +63523,7 @@
         <v>3</v>
       </c>
       <c r="F164" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="G164" cm="1">
         <f t="array" ref="G164">COUNT(IF(($A164=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63548,7 +63557,7 @@
         <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G165" cm="1">
         <f t="array" ref="G165">COUNT(IF(($A165=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63569,7 +63578,7 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>8</v>
@@ -63582,7 +63591,7 @@
         <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G166" cm="1">
         <f t="array" ref="G166">COUNT(IF(($A166=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63603,7 +63612,7 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>8</v>
@@ -63616,7 +63625,7 @@
         <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="G167" cm="1">
         <f t="array" ref="G167">COUNT(IF(($A167=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63650,7 +63659,7 @@
         <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G168" cm="1">
         <f t="array" ref="G168">COUNT(IF(($A168=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63684,7 +63693,7 @@
         <v>4</v>
       </c>
       <c r="F169" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G169" cm="1">
         <f t="array" ref="G169">COUNT(IF(($A169=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63718,7 +63727,7 @@
         <v>4</v>
       </c>
       <c r="F170" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G170" cm="1">
         <f t="array" ref="G170">COUNT(IF(($A170=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63752,10 +63761,10 @@
         <v>4</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F171" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G171" cm="1">
         <f t="array" ref="G171">COUNT(IF(($A171=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63789,7 +63798,7 @@
         <v>4</v>
       </c>
       <c r="F172" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G172" cm="1">
         <f t="array" ref="G172">COUNT(IF(($A172=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63823,7 +63832,7 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="G173" cm="1">
         <f t="array" ref="G173">COUNT(IF(($A173=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63844,7 +63853,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>8</v>
@@ -63857,10 +63866,10 @@
         <v>2</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F174" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G174" cm="1">
         <f t="array" ref="G174">COUNT(IF(($A174=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63894,7 +63903,7 @@
         <v>5</v>
       </c>
       <c r="F175" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G175" cm="1">
         <f t="array" ref="G175">COUNT(IF(($A175=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63928,7 +63937,7 @@
         <v>5</v>
       </c>
       <c r="F176" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G176" cm="1">
         <f t="array" ref="G176">COUNT(IF(($A176=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63962,10 +63971,10 @@
         <v>8</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F177" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G177" cm="1">
         <f t="array" ref="G177">COUNT(IF(($A177=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -63986,7 +63995,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>8</v>
@@ -63999,10 +64008,10 @@
         <v>6</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F178" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G178" cm="1">
         <f t="array" ref="G178">COUNT(IF(($A178=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64023,7 +64032,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>8</v>
@@ -64036,7 +64045,7 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G179" cm="1">
         <f t="array" ref="G179">COUNT(IF(($A179=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64070,10 +64079,10 @@
         <v>1</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F180" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G180" cm="1">
         <f t="array" ref="G180">COUNT(IF(($A180=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64107,7 +64116,7 @@
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="G181" cm="1">
         <f t="array" ref="G181">COUNT(IF(($A181=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64141,7 +64150,7 @@
         <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G182" cm="1">
         <f t="array" ref="G182">COUNT(IF(($A182=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64175,7 +64184,7 @@
         <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G183" cm="1">
         <f t="array" ref="G183">COUNT(IF(($A183=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64196,7 +64205,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>3</v>
@@ -64209,7 +64218,7 @@
         <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="G184" cm="1">
         <f t="array" ref="G184">COUNT(IF(($A184=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64243,7 +64252,7 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G185" cm="1">
         <f t="array" ref="G185">COUNT(IF(($A185=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64277,7 +64286,7 @@
         <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G186" cm="1">
         <f t="array" ref="G186">COUNT(IF(($A186=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64311,7 +64320,7 @@
         <v>3</v>
       </c>
       <c r="F187" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G187" cm="1">
         <f t="array" ref="G187">COUNT(IF(($A187=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64345,7 +64354,7 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G188" cm="1">
         <f t="array" ref="G188">COUNT(IF(($A188=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64379,7 +64388,7 @@
         <v>4</v>
       </c>
       <c r="F189" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="G189" cm="1">
         <f t="array" ref="G189">COUNT(IF(($A189=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64400,7 +64409,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>3</v>
@@ -64413,7 +64422,7 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="G190" cm="1">
         <f t="array" ref="G190">COUNT(IF(($A190=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64447,7 +64456,7 @@
         <v>5</v>
       </c>
       <c r="F191" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G191" cm="1">
         <f t="array" ref="G191">COUNT(IF(($A191=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64468,7 +64477,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>26</v>
@@ -64481,10 +64490,10 @@
         <v>1</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F192" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="G192" cm="1">
         <f t="array" ref="G192">COUNT(IF(($A192=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64518,10 +64527,10 @@
         <v>1</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F193" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G193" cm="1">
         <f t="array" ref="G193">COUNT(IF(($A193=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64555,7 +64564,7 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G194" cm="1">
         <f t="array" ref="G194">COUNT(IF(($A194=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64589,7 +64598,7 @@
         <v>2</v>
       </c>
       <c r="F195" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G195" cm="1">
         <f t="array" ref="G195">COUNT(IF(($A195=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64623,7 +64632,7 @@
         <v>2</v>
       </c>
       <c r="F196" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G196" cm="1">
         <f t="array" ref="G196">COUNT(IF(($A196=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64656,11 +64665,8 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="E197" s="1" t="s">
-        <v>1242</v>
-      </c>
       <c r="F197" t="s">
-        <v>1268</v>
+        <v>1490</v>
       </c>
       <c r="G197" cm="1">
         <f t="array" ref="G197">COUNT(IF(($A197=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64694,10 +64700,10 @@
         <v>2</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F198" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G198" cm="1">
         <f t="array" ref="G198">COUNT(IF(($A198=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64731,10 +64737,10 @@
         <v>3</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F199" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G199" cm="1">
         <f t="array" ref="G199">COUNT(IF(($A199=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64768,7 +64774,7 @@
         <v>4</v>
       </c>
       <c r="F200" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G200" cm="1">
         <f t="array" ref="G200">COUNT(IF(($A200=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64802,7 +64808,7 @@
         <v>4</v>
       </c>
       <c r="F201" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G201" cm="1">
         <f t="array" ref="G201">COUNT(IF(($A201=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64823,7 +64829,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>989</v>
+        <v>1488</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>26</v>
@@ -64836,10 +64842,10 @@
         <v>4</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F202" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="G202" cm="1">
         <f t="array" ref="G202">COUNT(IF(($A202=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64873,7 +64879,7 @@
         <v>5</v>
       </c>
       <c r="F203" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G203" cm="1">
         <f t="array" ref="G203">COUNT(IF(($A203=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64907,10 +64913,10 @@
         <v>7</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F204" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G204" cm="1">
         <f t="array" ref="G204">COUNT(IF(($A204=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64944,10 +64950,10 @@
         <v>7</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F205" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G205" cm="1">
         <f t="array" ref="G205">COUNT(IF(($A205=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -64968,7 +64974,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>26</v>
@@ -64981,10 +64987,10 @@
         <v>3</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F206" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="G206" cm="1">
         <f t="array" ref="G206">COUNT(IF(($A206=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65005,7 +65011,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>26</v>
@@ -65018,10 +65024,10 @@
         <v>3</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F207" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="G207" cm="1">
         <f t="array" ref="G207">COUNT(IF(($A207=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65042,7 +65048,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>26</v>
@@ -65055,7 +65061,7 @@
         <v>4</v>
       </c>
       <c r="F208" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G208" cm="1">
         <f t="array" ref="G208">COUNT(IF(($A208=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65076,7 +65082,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>26</v>
@@ -65089,7 +65095,7 @@
         <v>2</v>
       </c>
       <c r="F209" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G209" cm="1">
         <f t="array" ref="G209">COUNT(IF(($A209=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65123,7 +65129,7 @@
         <v>2</v>
       </c>
       <c r="F210" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="G210" cm="1">
         <f t="array" ref="G210">COUNT(IF(($A210=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65157,10 +65163,10 @@
         <v>2</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F211" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G211" cm="1">
         <f t="array" ref="G211">COUNT(IF(($A211=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65194,10 +65200,10 @@
         <v>3</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F212" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G212" cm="1">
         <f t="array" ref="G212">COUNT(IF(($A212=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65218,7 +65224,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B213" s="16" t="s">
         <v>33</v>
@@ -65231,10 +65237,10 @@
         <v>3</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F213" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G213" cm="1">
         <f t="array" ref="G213">COUNT(IF(($A213=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65255,7 +65261,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B214" s="16" t="s">
         <v>33</v>
@@ -65268,7 +65274,7 @@
         <v>4</v>
       </c>
       <c r="F214" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="G214" cm="1">
         <f t="array" ref="G214">COUNT(IF(($A214=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65302,7 +65308,7 @@
         <v>5</v>
       </c>
       <c r="F215" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G215" cm="1">
         <f t="array" ref="G215">COUNT(IF(($A215=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65336,7 +65342,7 @@
         <v>5</v>
       </c>
       <c r="F216" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="G216" cm="1">
         <f t="array" ref="G216">COUNT(IF(($A216=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65370,10 +65376,10 @@
         <v>8</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F217" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G217" cm="1">
         <f t="array" ref="G217">COUNT(IF(($A217=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65407,10 +65413,10 @@
         <v>6</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F218" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G218" cm="1">
         <f t="array" ref="G218">COUNT(IF(($A218=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65431,7 +65437,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B219" s="16" t="s">
         <v>33</v>
@@ -65444,7 +65450,7 @@
         <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="G219" cm="1">
         <f t="array" ref="G219">COUNT(IF(($A219=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65465,7 +65471,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B220" s="16" t="s">
         <v>33</v>
@@ -65478,10 +65484,10 @@
         <v>2</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F220" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G220" cm="1">
         <f t="array" ref="G220">COUNT(IF(($A220=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65502,7 +65508,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B221" s="16" t="s">
         <v>33</v>
@@ -65515,10 +65521,10 @@
         <v>4</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F221" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G221" cm="1">
         <f t="array" ref="G221">COUNT(IF(($A221=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65539,7 +65545,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B222" s="16" t="s">
         <v>33</v>
@@ -65552,10 +65558,10 @@
         <v>2</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F222" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G222" cm="1">
         <f t="array" ref="G222">COUNT(IF(($A222=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65589,10 +65595,10 @@
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F223" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G223" cm="1">
         <f t="array" ref="G223">COUNT(IF(($A223=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65626,10 +65632,10 @@
         <v>1</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F224" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="G224" cm="1">
         <f t="array" ref="G224">COUNT(IF(($A224=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65663,10 +65669,10 @@
         <v>2</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F225" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G225" cm="1">
         <f t="array" ref="G225">COUNT(IF(($A225=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65700,10 +65706,10 @@
         <v>1</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F226" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G226" cm="1">
         <f t="array" ref="G226">COUNT(IF(($A226=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65737,7 +65743,7 @@
         <v>3</v>
       </c>
       <c r="F227" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G227" cm="1">
         <f t="array" ref="G227">COUNT(IF(($A227=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65758,7 +65764,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B228" s="20" t="s">
         <v>39</v>
@@ -65771,10 +65777,10 @@
         <v>3</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F228" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G228" cm="1">
         <f t="array" ref="G228">COUNT(IF(($A228=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65808,7 +65814,7 @@
         <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G229" cm="1">
         <f t="array" ref="G229">COUNT(IF(($A229=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65842,7 +65848,7 @@
         <v>3</v>
       </c>
       <c r="F230" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G230" cm="1">
         <f t="array" ref="G230">COUNT(IF(($A230=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65876,7 +65882,7 @@
         <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G231" cm="1">
         <f t="array" ref="G231">COUNT(IF(($A231=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65910,7 +65916,7 @@
         <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G232" cm="1">
         <f t="array" ref="G232">COUNT(IF(($A232=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65931,7 +65937,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B233" s="20" t="s">
         <v>39</v>
@@ -65944,7 +65950,7 @@
         <v>4</v>
       </c>
       <c r="F233" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G233" cm="1">
         <f t="array" ref="G233">COUNT(IF(($A233=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -65952,11 +65958,11 @@
       </c>
       <c r="H233" cm="1">
         <f t="array" ref="H233">MIN(IF(($A233=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I233" cm="1">
         <f t="array" ref="I233">MAX(IF(($A233=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J233">
         <f t="shared" si="12"/>
@@ -65978,10 +65984,10 @@
         <v>5</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F234" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G234" cm="1">
         <f t="array" ref="G234">COUNT(IF(($A234=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66015,10 +66021,10 @@
         <v>6</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F235" s="26" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G235" cm="1">
         <f t="array" ref="G235">COUNT(IF(($A235=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66049,10 +66055,10 @@
         <v/>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F236" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="G236" cm="1">
         <f t="array" ref="G236">COUNT(IF(($A236=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66073,7 +66079,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B237" s="20" t="s">
         <v>39</v>
@@ -66086,7 +66092,7 @@
         <v>3</v>
       </c>
       <c r="F237" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G237" cm="1">
         <f t="array" ref="G237">COUNT(IF(($A237=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66107,7 +66113,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B238" s="20" t="s">
         <v>39</v>
@@ -66120,10 +66126,10 @@
         <v>4</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F238" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G238" cm="1">
         <f t="array" ref="G238">COUNT(IF(($A238=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66144,7 +66150,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B239" s="20" t="s">
         <v>39</v>
@@ -66157,10 +66163,10 @@
         <v>6</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F239" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="G239" cm="1">
         <f t="array" ref="G239">COUNT(IF(($A239=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66194,7 +66200,7 @@
         <v>3</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F240" t="s">
         <v>562</v>
@@ -66231,7 +66237,7 @@
         <v>4</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F241" t="s">
         <v>562</v>
@@ -66268,7 +66274,7 @@
         <v>4</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F242" t="s">
         <v>784</v>
@@ -66305,10 +66311,10 @@
         <v>6</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F243" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G243" cm="1">
         <f t="array" ref="G243">COUNT(IF(($A243=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66342,7 +66348,7 @@
         <v>5</v>
       </c>
       <c r="F244" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G244" cm="1">
         <f t="array" ref="G244">COUNT(IF(($A244=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66373,10 +66379,10 @@
         <v/>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F245" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G245" cm="1">
         <f t="array" ref="G245">COUNT(IF(($A245=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66407,10 +66413,10 @@
         <v/>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F246" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="G246" cm="1">
         <f t="array" ref="G246">COUNT(IF(($A246=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66444,10 +66450,10 @@
         <v>2</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F247" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G247" cm="1">
         <f t="array" ref="G247">COUNT(IF(($A247=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66481,7 +66487,7 @@
         <v>2</v>
       </c>
       <c r="F248" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G248" cm="1">
         <f t="array" ref="G248">COUNT(IF(($A248=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66515,7 +66521,7 @@
         <v>3</v>
       </c>
       <c r="F249" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G249" cm="1">
         <f t="array" ref="G249">COUNT(IF(($A249=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66549,7 +66555,7 @@
         <v>3</v>
       </c>
       <c r="F250" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G250" cm="1">
         <f t="array" ref="G250">COUNT(IF(($A250=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66583,10 +66589,10 @@
         <v>3</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F251" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G251" cm="1">
         <f t="array" ref="G251">COUNT(IF(($A251=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66620,7 +66626,7 @@
         <v>3</v>
       </c>
       <c r="F252" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G252" cm="1">
         <f t="array" ref="G252">COUNT(IF(($A252=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66654,7 +66660,7 @@
         <v>4</v>
       </c>
       <c r="F253" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G253" cm="1">
         <f t="array" ref="G253">COUNT(IF(($A253=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66688,10 +66694,10 @@
         <v>4</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F254" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G254" cm="1">
         <f t="array" ref="G254">COUNT(IF(($A254=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66725,7 +66731,7 @@
         <v>4</v>
       </c>
       <c r="F255" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="G255" cm="1">
         <f t="array" ref="G255">COUNT(IF(($A255=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66759,7 +66765,7 @@
         <v>2</v>
       </c>
       <c r="F256" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="G256" cm="1">
         <f t="array" ref="G256">COUNT(IF(($A256=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66793,7 +66799,7 @@
         <v>4</v>
       </c>
       <c r="F257" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G257" cm="1">
         <f t="array" ref="G257">COUNT(IF(($A257=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66827,7 +66833,7 @@
         <v>5</v>
       </c>
       <c r="F258" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G258" cm="1">
         <f t="array" ref="G258">COUNT(IF(($A258=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66861,7 +66867,7 @@
         <v>5</v>
       </c>
       <c r="F259" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G259" cm="1">
         <f t="array" ref="G259">COUNT(IF(($A259=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66882,23 +66888,23 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B260" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C260">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D260">
         <f t="shared" si="15"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F260" t="s">
-        <v>1258</v>
+        <v>1489</v>
       </c>
       <c r="G260" cm="1">
         <f t="array" ref="G260">COUNT(IF(($A260=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66906,11 +66912,11 @@
       </c>
       <c r="H260" cm="1">
         <f t="array" ref="H260">MIN(IF(($A260=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I260" cm="1">
         <f t="array" ref="I260">MAX(IF(($A260=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J260">
         <f t="shared" si="12"/>
@@ -66919,7 +66925,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B261" s="7" t="s">
         <v>6</v>
@@ -66932,7 +66938,7 @@
         <v>5</v>
       </c>
       <c r="F261" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="G261" cm="1">
         <f t="array" ref="G261">COUNT(IF(($A261=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66953,7 +66959,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B262" s="13" t="s">
         <v>5</v>
@@ -66966,10 +66972,10 @@
         <v>5</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F262" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="G262" cm="1">
         <f t="array" ref="G262">COUNT(IF(($A262=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -66990,7 +66996,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>26</v>
@@ -67003,10 +67009,10 @@
         <v>4</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1219</v>
+        <v>1241</v>
       </c>
       <c r="F263" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="G263" cm="1">
         <f t="array" ref="G263">COUNT(IF(($A263=pokemon!$AC$2:$AC$415)*(pokemon!$D$2:$D$415 &lt;&gt; "Noble Form")*(ISBLANK(pokemon!$AK$2:$AK$415)), pokemon!$V$2:$V$415))</f>
@@ -67915,7 +67921,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D37" t="s">
         <v>599</v>
@@ -67927,7 +67933,7 @@
         <v>601</v>
       </c>
       <c r="G37" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H37" t="s">
         <v>557</v>
@@ -68802,16 +68808,16 @@
         <v>843</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68819,16 +68825,16 @@
         <v>847</v>
       </c>
       <c r="B2" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D2" t="s">
         <v>848</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68836,16 +68842,16 @@
         <v>900</v>
       </c>
       <c r="B3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D3" t="s">
         <v>877</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -68856,13 +68862,13 @@
         <v>897</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D4" t="s">
         <v>898</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68870,16 +68876,16 @@
         <v>933</v>
       </c>
       <c r="B5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>1065</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68893,7 +68899,7 @@
         <v>904</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68904,13 +68910,13 @@
         <v>880</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D7" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68921,13 +68927,13 @@
         <v>882</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68935,16 +68941,16 @@
         <v>852</v>
       </c>
       <c r="B9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D9" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -68952,16 +68958,16 @@
         <v>931</v>
       </c>
       <c r="B10" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>1288</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68972,13 +68978,13 @@
         <v>918</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D11" t="s">
         <v>919</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -68986,16 +68992,16 @@
         <v>886</v>
       </c>
       <c r="B12" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D12" t="s">
         <v>888</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -69006,30 +69012,30 @@
         <v>863</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D13" t="s">
         <v>864</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D14" t="s">
         <v>1097</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1098</v>
-      </c>
       <c r="E14" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69040,13 +69046,13 @@
         <v>881</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D15" t="s">
         <v>899</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69057,7 +69063,7 @@
         <v>901</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -69068,13 +69074,13 @@
         <v>845</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D17" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69082,16 +69088,16 @@
         <v>929</v>
       </c>
       <c r="B18" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D18" t="s">
         <v>935</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69099,30 +69105,30 @@
         <v>891</v>
       </c>
       <c r="B19" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D19" t="s">
         <v>1311</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>1312</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B20" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D20" t="s">
         <v>1314</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1316</v>
-      </c>
       <c r="E20" s="23" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="75" x14ac:dyDescent="0.25">
@@ -69133,7 +69139,7 @@
         <v>924</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D21" t="s">
         <v>909</v>
@@ -69147,16 +69153,16 @@
         <v>859</v>
       </c>
       <c r="B22" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D22" t="s">
         <v>902</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69167,13 +69173,13 @@
         <v>850</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D23" t="s">
         <v>851</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -69184,13 +69190,13 @@
         <v>893</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D24" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69198,16 +69204,16 @@
         <v>860</v>
       </c>
       <c r="B25" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="D25" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69218,13 +69224,13 @@
         <v>858</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69232,16 +69238,16 @@
         <v>894</v>
       </c>
       <c r="B27" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="D27" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="75" x14ac:dyDescent="0.25">
@@ -69252,13 +69258,13 @@
         <v>916</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D28" t="s">
         <v>917</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69266,16 +69272,16 @@
         <v>927</v>
       </c>
       <c r="B29" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D29" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69283,16 +69289,16 @@
         <v>906</v>
       </c>
       <c r="B30" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D30" t="s">
         <v>907</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69300,10 +69306,10 @@
         <v>865</v>
       </c>
       <c r="D31" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69311,16 +69317,16 @@
         <v>846</v>
       </c>
       <c r="B32" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>1337</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>1340</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69328,16 +69334,16 @@
         <v>866</v>
       </c>
       <c r="B33" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>1346</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69348,13 +69354,13 @@
         <v>885</v>
       </c>
       <c r="C34" s="23" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E34" s="23" t="s">
         <v>1341</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69365,13 +69371,13 @@
         <v>937</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D35" t="s">
         <v>936</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69379,16 +69385,16 @@
         <v>871</v>
       </c>
       <c r="B36" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D36" t="s">
         <v>872</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69396,16 +69402,16 @@
         <v>855</v>
       </c>
       <c r="B37" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="D37" t="s">
         <v>856</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -69416,13 +69422,13 @@
         <v>922</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D38" t="s">
         <v>926</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69433,13 +69439,13 @@
         <v>934</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D39" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69447,16 +69453,16 @@
         <v>853</v>
       </c>
       <c r="B40" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D40" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69467,13 +69473,13 @@
         <v>883</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D41" t="s">
         <v>875</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69484,13 +69490,13 @@
         <v>884</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D42" t="s">
         <v>876</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -69501,7 +69507,7 @@
         <v>868</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D43" t="s">
         <v>869</v>
@@ -69515,13 +69521,13 @@
         <v>932</v>
       </c>
       <c r="B44" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69529,16 +69535,16 @@
         <v>889</v>
       </c>
       <c r="B45" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D45" t="s">
         <v>890</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69546,16 +69552,16 @@
         <v>911</v>
       </c>
       <c r="B46" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D46" t="s">
         <v>920</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -69563,16 +69569,16 @@
         <v>910</v>
       </c>
       <c r="B47" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D47" t="s">
         <v>923</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -69580,33 +69586,33 @@
         <v>887</v>
       </c>
       <c r="B48" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C48" s="23" t="s">
         <v>1092</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="D48" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E48" s="23" t="s">
         <v>1093</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B49" t="s">
         <v>1123</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="23" t="s">
         <v>1124</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="D49" t="s">
         <v>1125</v>
       </c>
-      <c r="D49" t="s">
-        <v>1126</v>
-      </c>
       <c r="E49" s="23" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
   </sheetData>
